--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488259_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488259_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0686</v>
+        <v>3.3011</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7778</v>
+        <v>1.8872</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2908</v>
+        <v>1.4139</v>
       </c>
       <c r="G2" t="n">
         <v>1.3391</v>
@@ -610,13 +610,13 @@
         <v>1.297</v>
       </c>
       <c r="S2" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.3146</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2773</v>
+        <v>-0.1679</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3594</v>
+        <v>0.4825</v>
       </c>
       <c r="V2" t="n">
         <v>2.2033</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7268</v>
+        <v>2.0069</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0121</v>
+        <v>2.4153</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2853</v>
+        <v>-0.4084</v>
       </c>
       <c r="G3" t="n">
         <v>0.8129999999999999</v>
@@ -688,13 +688,13 @@
         <v>1.297</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2462</v>
+        <v>0.5263</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4414</v>
+        <v>-0.0382</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6877</v>
+        <v>0.5645</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6294</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. VIOQUE LOMBARDO</t>
+          <t>M. RAMOS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5672</v>
+        <v>1.6117</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0969</v>
+        <v>0.6296</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5296999999999999</v>
+        <v>0.9822</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0169</v>
+        <v>1.0756</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8478</v>
+        <v>1.2813</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8647</v>
+        <v>-0.2057</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8284</v>
+        <v>0.6136</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.52</v>
+        <v>0.4891</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3484</v>
+        <v>0.1244</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8115</v>
+        <v>0.462</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3278</v>
+        <v>0.7922</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4837</v>
+        <v>-0.3301</v>
       </c>
       <c r="P4" t="n">
         <v>1.1117</v>
@@ -766,28 +766,28 @@
         <v>1.1117</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6974</v>
+        <v>-0.2611</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2684</v>
+        <v>-0.2984</v>
       </c>
       <c r="U4" t="n">
-        <v>0.429</v>
+        <v>0.0373</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2589</v>
+        <v>-0.3144</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2589</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. RAMOS RODRIGUEZ</t>
+          <t>P. SECO LOPEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0668</v>
+        <v>1.2466</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1831</v>
+        <v>0.8599</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8837</v>
+        <v>0.3868</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0756</v>
+        <v>1.8406</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2813</v>
+        <v>2.1309</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2057</v>
+        <v>-0.2903</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6136</v>
+        <v>2.4461</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4891</v>
+        <v>1.7305</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1244</v>
+        <v>0.7157</v>
       </c>
       <c r="M5" t="n">
-        <v>0.462</v>
+        <v>-0.6056</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7922</v>
+        <v>0.4004</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3301</v>
+        <v>-1.006</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1117</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R5" t="n">
         <v>1.1117</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8061</v>
+        <v>-0.1673</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7449</v>
+        <v>-0.0479</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0612</v>
+        <v>-0.1194</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3144</v>
+        <v>0.3144</v>
       </c>
       <c r="W5" t="n">
         <v>0.3144</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. DOBLADO GARCIA</t>
+          <t>I. VIOQUE LOMBARDO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0311</v>
+        <v>1.0458</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8938</v>
+        <v>1.5755</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9249</v>
+        <v>-0.5296999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.6092</v>
+        <v>0.0169</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3894</v>
+        <v>-0.8478</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.2197</v>
+        <v>0.8647</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.6045</v>
+        <v>0.8284</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.108</v>
+        <v>-0.52</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.4965</v>
+        <v>1.3484</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0047</v>
+        <v>-0.8115</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2814</v>
+        <v>-0.3278</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2767</v>
+        <v>-0.4837</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1853</v>
+        <v>1.1117</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6676</v>
+        <v>1.1117</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9928</v>
+        <v>1.1761</v>
       </c>
       <c r="T6" t="n">
-        <v>0.102</v>
+        <v>0.7471</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8908</v>
+        <v>0.429</v>
       </c>
       <c r="V6" t="n">
-        <v>2.8327</v>
+        <v>-1.2589</v>
       </c>
       <c r="W6" t="n">
-        <v>3.4616</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6289</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LLANO ABASCAL</t>
+          <t>A. DOBLADO GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9881</v>
+        <v>0.8024</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0772</v>
+        <v>-0.9255</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0891</v>
+        <v>1.7279</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2951</v>
+        <v>-2.6092</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1247</v>
+        <v>-0.3894</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1704</v>
+        <v>-2.2197</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-2.6045</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.5251</v>
+        <v>-0.108</v>
       </c>
       <c r="L7" t="n">
-        <v>0.705</v>
+        <v>-2.4965</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.475</v>
+        <v>-0.0047</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4004</v>
+        <v>-0.2814</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8754</v>
+        <v>0.2767</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9264</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9264</v>
+        <v>1.6676</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0423</v>
+        <v>0.7641</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2684</v>
+        <v>0.0703</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2261</v>
+        <v>0.6939</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3144</v>
+        <v>2.8327</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6289</v>
+        <v>3.4616</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3144</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. SECO LOPEZ</t>
+          <t>A. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5359</v>
+        <v>0.4071</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2723</v>
+        <v>0.3485</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2637</v>
+        <v>0.0587</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8406</v>
+        <v>-1.2951</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1309</v>
+        <v>-1.1247</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2903</v>
+        <v>-0.1704</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4461</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7305</v>
+        <v>-1.5251</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7157</v>
+        <v>0.705</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6056</v>
+        <v>-0.475</v>
       </c>
       <c r="N8" t="n">
         <v>0.4004</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.006</v>
+        <v>-0.8754</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1117</v>
+        <v>0.9264</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8779</v>
+        <v>0.4614</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6354</v>
+        <v>0.5397</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2425</v>
+        <v>-0.0784</v>
       </c>
       <c r="V8" t="n">
         <v>0.3144</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3144</v>
+        <v>0.6289</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="9">
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. POL RUBIO</t>
+          <t>A. DIAZ MACIAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6731</v>
+        <v>-0.5004</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6518</v>
+        <v>-0.5355</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3249</v>
+        <v>0.0351</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6835</v>
+        <v>1.1046</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1735</v>
+        <v>0.5745</v>
       </c>
       <c r="I10" t="n">
-        <v>0.51</v>
+        <v>0.5301</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7065</v>
+        <v>1.3093</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0429</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6635</v>
+        <v>0.7986</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.023</v>
+        <v>-0.2047</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1306</v>
+        <v>0.0639</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1536</v>
+        <v>-0.2686</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-2.594</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3.7057</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0977</v>
+        <v>0.6746</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0547</v>
+        <v>-0.0267</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.043</v>
+        <v>0.7013</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2589</v>
+        <v>0.3144</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.8877</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2589</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. DIAZ MACIAS</t>
+          <t>D. POL RUBIO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7865</v>
+        <v>-0.6239</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8955</v>
+        <v>0.6518</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1089</v>
+        <v>-1.2756</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1046</v>
+        <v>0.6835</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5745</v>
+        <v>0.1735</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5301</v>
+        <v>0.51</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3093</v>
+        <v>0.7065</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.0429</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7986</v>
+        <v>0.6635</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2047</v>
+        <v>-0.023</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0639</v>
+        <v>0.1306</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2686</v>
+        <v>-0.1536</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.594</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3885</v>
+        <v>-0.0485</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3867</v>
+        <v>-0.0547</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7752</v>
+        <v>0.0062</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3144</v>
+        <v>-1.2589</v>
       </c>
       <c r="W11" t="n">
-        <v>1.8877</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5733</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. VIOQUE LOMBARDO</t>
+          <t>P. CORREA GALLARDO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6915</v>
+        <v>-1.517</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8946</v>
+        <v>-1.1817</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2031</v>
+        <v>-0.3353</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.3847</v>
+        <v>1.1557</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7028</v>
+        <v>0.2664</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.0875</v>
+        <v>0.8894</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0403</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1718</v>
+        <v>0.0429</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2121</v>
+        <v>0.6742</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3444</v>
+        <v>0.4386</v>
       </c>
       <c r="N12" t="n">
-        <v>0.531</v>
+        <v>0.2234</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8754</v>
+        <v>0.2152</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3706</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R12" t="n">
-        <v>1.297</v>
+        <v>0.1853</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0485</v>
+        <v>0.2537</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0721</v>
+        <v>-0.046</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1206</v>
+        <v>0.2997</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6289</v>
+        <v>-1.2589</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6289</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. CORREA GALLARDO</t>
+          <t>J. VIOQUE LOMBARDO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8841</v>
+        <v>-2.0105</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.5734</v>
+        <v>-2.0905</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3107</v>
+        <v>0.08</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1557</v>
+        <v>-1.3847</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2664</v>
+        <v>0.7028</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8894</v>
+        <v>-2.0875</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7171999999999999</v>
+        <v>-1.0403</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0429</v>
+        <v>0.1718</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6742</v>
+        <v>-1.2121</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4386</v>
+        <v>-0.3444</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2234</v>
+        <v>0.531</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2152</v>
+        <v>-0.8754</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.6676</v>
+        <v>0.3706</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1853</v>
+        <v>1.297</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1134</v>
+        <v>-0.3675</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4377</v>
+        <v>-0.1237</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3243</v>
+        <v>-0.2437</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2589</v>
+        <v>-0.6289</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2589</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2714</v>
+        <v>6.091900000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>3.136000000000001</v>
+        <v>3.956699999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>2.135400000000001</v>
+        <v>2.1356</v>
       </c>
       <c r="G14" t="n">
         <v>3.0621</v>
@@ -1516,16 +1516,16 @@
         <v>3.83</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7676999999999996</v>
+        <v>-0.7676999999999998</v>
       </c>
       <c r="J14" t="n">
-        <v>5.692599999999999</v>
+        <v>5.692600000000001</v>
       </c>
       <c r="K14" t="n">
         <v>2.1612</v>
       </c>
       <c r="L14" t="n">
-        <v>3.531100000000001</v>
+        <v>3.5311</v>
       </c>
       <c r="M14" t="n">
         <v>-2.6305</v>
@@ -1534,7 +1534,7 @@
         <v>1.6687</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.2991</v>
+        <v>-4.299100000000001</v>
       </c>
       <c r="P14" t="n">
         <v>-0.9265000000000001</v>
@@ -1546,13 +1546,13 @@
         <v>11.1171</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5057</v>
+        <v>3.326399999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2671999999999999</v>
+        <v>0.5536</v>
       </c>
       <c r="U14" t="n">
-        <v>2.773</v>
+        <v>2.7729</v>
       </c>
       <c r="V14" t="n">
         <v>0.6298000000000008</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2419</v>
+        <v>4.2739</v>
       </c>
       <c r="E15" t="n">
         <v>2.1006</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1412</v>
+        <v>2.1733</v>
       </c>
       <c r="G15" t="n">
         <v>4.0229</v>
@@ -1624,13 +1624,13 @@
         <v>0.7411</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0898</v>
+        <v>0.1219</v>
       </c>
       <c r="T15" t="n">
         <v>0.051</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0388</v>
+        <v>0.0709</v>
       </c>
       <c r="V15" t="n">
         <v>0.3144</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. VALDES ALVAREZ</t>
+          <t>A. RODRIGUEZ TORRERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6722</v>
+        <v>3.31</v>
       </c>
       <c r="E16" t="n">
-        <v>4.3721</v>
+        <v>0.6863</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6998</v>
+        <v>2.6237</v>
       </c>
       <c r="G16" t="n">
-        <v>1.173</v>
+        <v>0.1613</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1467</v>
+        <v>-0.9355</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0263</v>
+        <v>1.0967</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3694</v>
+        <v>-0.9715</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1205</v>
+        <v>-1.7915</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2488</v>
+        <v>0.82</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1964</v>
+        <v>1.1328</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0262</v>
+        <v>0.856</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2226</v>
+        <v>0.2767</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6676</v>
+        <v>1.297</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6676</v>
+        <v>2.2234</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2017</v>
+        <v>-0.351</v>
       </c>
       <c r="T16" t="n">
-        <v>0.485</v>
+        <v>-0.5624</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2833</v>
+        <v>0.2114</v>
       </c>
       <c r="V16" t="n">
-        <v>0.63</v>
+        <v>2.2027</v>
       </c>
       <c r="W16" t="n">
-        <v>2.5177</v>
+        <v>3.1466</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.8877</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ TORRERO</t>
+          <t>C. VALDES ALVAREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.4262</v>
+        <v>3.2398</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5883</v>
+        <v>3.7845</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8378</v>
+        <v>-0.5446</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1613</v>
+        <v>1.173</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9355</v>
+        <v>1.1467</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0967</v>
+        <v>0.0263</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9715</v>
+        <v>1.3694</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.7915</v>
+        <v>1.1205</v>
       </c>
       <c r="L17" t="n">
-        <v>0.82</v>
+        <v>0.2488</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1328</v>
+        <v>-0.1964</v>
       </c>
       <c r="N17" t="n">
-        <v>0.856</v>
+        <v>0.0262</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2767</v>
+        <v>-0.2226</v>
       </c>
       <c r="P17" t="n">
-        <v>1.297</v>
+        <v>1.6676</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2234</v>
+        <v>1.6676</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2348</v>
+        <v>-0.2307</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6603</v>
+        <v>-0.1026</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4255</v>
+        <v>-0.1281</v>
       </c>
       <c r="V17" t="n">
-        <v>2.2027</v>
+        <v>0.63</v>
       </c>
       <c r="W17" t="n">
-        <v>3.1466</v>
+        <v>2.5177</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.9439</v>
+        <v>-1.8877</v>
       </c>
     </row>
     <row r="18">
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. LATORRE SANCHEZ</t>
+          <t>B. VIDAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2323</v>
+        <v>-0.4728</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7144</v>
+        <v>-0.3933</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9467</v>
+        <v>-0.0795</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8626</v>
+        <v>0.0366</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5263</v>
+        <v>0.2362</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3363</v>
+        <v>-0.1996</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7765</v>
+        <v>0.0127</v>
       </c>
       <c r="K19" t="n">
-        <v>0.408</v>
+        <v>0.0127</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3686</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.6391</v>
+        <v>0.0239</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9343</v>
+        <v>0.2234</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.7048</v>
+        <v>-0.1996</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1853</v>
+        <v>0.3706</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1117</v>
+        <v>0.3706</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0744</v>
+        <v>-0.2506</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8643</v>
+        <v>-0.406</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2101</v>
+        <v>0.1554</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6294</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. VIDAL</t>
+          <t>A. GONZALEZ PALOMO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7671</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5891</v>
+        <v>-0.0504</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.178</v>
+        <v>-0.6487000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0366</v>
+        <v>2.2939</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2362</v>
+        <v>-0.5228</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1996</v>
+        <v>2.8168</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0127</v>
+        <v>2.1221</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0127</v>
+        <v>-0.5026</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.6246</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0239</v>
+        <v>0.1719</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2234</v>
+        <v>-0.0203</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1996</v>
+        <v>0.1922</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3706</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3706</v>
+        <v>1.4823</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5449000000000001</v>
+        <v>-0.4203</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6019</v>
+        <v>-0.3196</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0569</v>
+        <v>-0.1007</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6294</v>
+        <v>-2.2022</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6294</v>
+        <v>-2.2022</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GONZALEZ PALOMO</t>
+          <t>J. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9677</v>
+        <v>-1.2116</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4421</v>
+        <v>0.7351</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5256</v>
+        <v>-1.9467</v>
       </c>
       <c r="G21" t="n">
-        <v>2.2939</v>
+        <v>-0.8626</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5228</v>
+        <v>-0.5263</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8168</v>
+        <v>-0.3363</v>
       </c>
       <c r="J21" t="n">
-        <v>2.1221</v>
+        <v>1.7765</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5026</v>
+        <v>0.408</v>
       </c>
       <c r="L21" t="n">
-        <v>2.6246</v>
+        <v>1.3686</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1719</v>
+        <v>-2.6391</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0203</v>
+        <v>-0.9343</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1922</v>
+        <v>-1.7048</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3706</v>
+        <v>0.1853</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4823</v>
+        <v>1.1117</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6889</v>
+        <v>0.0951</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7113</v>
+        <v>-0.115</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0224</v>
+        <v>0.2101</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.2022</v>
+        <v>-0.6294</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.2022</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. GOMEZ MORENO</t>
+          <t>R. FREIRE DELTIO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.172</v>
+        <v>-1.3339</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2239</v>
+        <v>-0.1378</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9481000000000001</v>
+        <v>-1.1961</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9062</v>
+        <v>-1.3723</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.5744</v>
+        <v>-0.0789</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3318</v>
+        <v>-1.2934</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5484</v>
+        <v>0.1385</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6314</v>
+        <v>0.6871</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0829</v>
+        <v>-0.5486</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3577</v>
+        <v>-1.5108</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9429999999999999</v>
+        <v>-0.766</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4147</v>
+        <v>-0.7448</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1853</v>
+        <v>0.7411</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1853</v>
+        <v>0.7411</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5489000000000001</v>
+        <v>-0.3883</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3246</v>
+        <v>-0.2764</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2243</v>
+        <v>-0.1119</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. GIL VARGAS</t>
+          <t>P. GOMEZ MORENO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7101</v>
+        <v>-1.4417</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0891</v>
+        <v>-0.4197</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6211</v>
+        <v>-1.022</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-1.9062</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0643</v>
+        <v>-1.5744</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1382</v>
+        <v>-0.3318</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4392</v>
+        <v>-0.5484</v>
       </c>
       <c r="K23" t="n">
-        <v>1.0092</v>
+        <v>-0.6314</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5699</v>
+        <v>0.0829</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5131</v>
+        <v>-1.3577</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0552</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5683</v>
+        <v>-0.4147</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.6676</v>
+        <v>0.1853</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0.1853</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0313</v>
+        <v>0.2792</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3246</v>
+        <v>0.1287</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2932</v>
+        <v>0.1505</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. FREIRE DELTIO</t>
+          <t>G. GIL VARGAS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8728</v>
+        <v>-1.6277</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-1.2849</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2453</v>
+        <v>-0.3428</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.3723</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0789</v>
+        <v>1.0643</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2934</v>
+        <v>-1.1382</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1385</v>
+        <v>0.4392</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6871</v>
+        <v>1.0092</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5486</v>
+        <v>-0.5699</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5108</v>
+        <v>-0.5131</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.766</v>
+        <v>0.0552</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7448</v>
+        <v>-0.5683</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7411</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7411</v>
+        <v>0.1853</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9272</v>
+        <v>0.1138</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.766</v>
+        <v>0.1287</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1612</v>
+        <v>-0.0149</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.0296</v>
+        <v>-1.899</v>
       </c>
       <c r="E25" t="n">
         <v>-1.0765</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9530999999999999</v>
+        <v>-0.8225</v>
       </c>
       <c r="G25" t="n">
         <v>-0.699</v>
@@ -2404,13 +2404,13 @@
         <v>0.3706</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1517</v>
+        <v>0.2823</v>
       </c>
       <c r="T25" t="n">
         <v>-0.0037</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1554</v>
+        <v>0.286</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.6443</v>
+        <v>-2.3253</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.5691</v>
+        <v>-3.3733</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9248</v>
+        <v>1.0479</v>
       </c>
       <c r="G26" t="n">
         <v>-2.5805</v>
@@ -2482,13 +2482,13 @@
         <v>0.9264</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6926</v>
+        <v>-0.3737</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.766</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.1965</v>
       </c>
       <c r="V26" t="n">
         <v>0.6289</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.8377</v>
+        <v>-5.0532</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.9157</v>
+        <v>-3.3281</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.922</v>
+        <v>-1.7251</v>
       </c>
       <c r="G27" t="n">
         <v>-3.8774</v>
@@ -2560,13 +2560,13 @@
         <v>2.0382</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.5151</v>
+        <v>-0.7306</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.3132</v>
+        <v>-0.7256</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.202</v>
+        <v>-0.005</v>
       </c>
       <c r="V27" t="n">
         <v>-0.6304999999999999</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-5.271199999999999</v>
+        <v>-4.618499999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.1355</v>
+        <v>-2.1354</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.1359</v>
+        <v>-2.483100000000001</v>
       </c>
       <c r="G28" t="n">
         <v>-3.0621</v>
@@ -2611,7 +2611,7 @@
         <v>0.7678999999999996</v>
       </c>
       <c r="J28" t="n">
-        <v>2.630399999999999</v>
+        <v>2.630400000000001</v>
       </c>
       <c r="K28" t="n">
         <v>-1.6688</v>
@@ -2620,16 +2620,16 @@
         <v>4.299100000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>-5.692400000000001</v>
+        <v>-5.692399999999999</v>
       </c>
       <c r="N28" t="n">
         <v>-2.1613</v>
       </c>
       <c r="O28" t="n">
-        <v>-3.5313</v>
+        <v>-3.531300000000001</v>
       </c>
       <c r="P28" t="n">
-        <v>0.9264000000000003</v>
+        <v>0.9263999999999999</v>
       </c>
       <c r="Q28" t="n">
         <v>-11.1172</v>
@@ -2638,13 +2638,13 @@
         <v>12.0436</v>
       </c>
       <c r="S28" t="n">
-        <v>-2.5057</v>
+        <v>-1.8529</v>
       </c>
       <c r="T28" t="n">
-        <v>-2.7729</v>
+        <v>-2.773</v>
       </c>
       <c r="U28" t="n">
-        <v>0.2671000000000001</v>
+        <v>0.9201999999999999</v>
       </c>
       <c r="V28" t="n">
         <v>-0.6298999999999998</v>
@@ -2653,7 +2653,7 @@
         <v>9.1242</v>
       </c>
       <c r="X28" t="n">
-        <v>-9.754100000000001</v>
+        <v>-9.754099999999999</v>
       </c>
     </row>
   </sheetData>
